--- a/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -413,8 +413,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
+      <c r="D2">
+        <v>24.9</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -427,8 +427,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>21.3</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
+      <c r="D4">
+        <v>22.6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>20.6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -469,8 +469,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
+      <c r="D6">
+        <v>21.4</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -484,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -777,8 +777,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
-        <v>4</v>
+      <c r="D28">
+        <v>18.7</v>
       </c>
     </row>
     <row r="29" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>4</v>
+      <c r="D13">
+        <v>19.9</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>19.1</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -777,8 +777,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28">
-        <v>18.7</v>
+      <c r="D28" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>19.9</v>
+      <c r="D13" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15">
-        <v>19.1</v>
+      <c r="D15" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
